--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -1,34 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1C2A1C-3FF4-4943-A6DD-E8DD98B243E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Inspector</t>
+  </si>
+  <si>
+    <t>Sede</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>Ítems</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +71,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,120 +373,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Inspector</t>
-        </is>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Sede</t>
-        </is>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Ítems</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ARIZA MARIN SERGIO</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CALDAS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>prueba</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Stickers 🔵</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CRISTIAN CHICA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CALDAS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>prueba</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Papelería general 📦</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CRISTIAN CHICA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CALDAS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>prueba</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Stickers 🔵</t>
-        </is>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -1,58 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1C2A1C-3FF4-4943-A6DD-E8DD98B243E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Inspector</t>
-  </si>
-  <si>
-    <t>Sede</t>
-  </si>
-  <si>
-    <t>Responsable</t>
-  </si>
-  <si>
-    <t>Ítems</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -71,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -373,25 +408,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Inspector</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Sede</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Ítems</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VILLA LOAIZA JHEISON ESTIBEN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>JUAN DIEGO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Guantes 🧤</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,33 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Guantes 🧤</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VILLA LOAIZA JHEISON ESTIBEN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PRUEBA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
     </row>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -1,34 +1,85 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E4E12E-147E-43B3-980C-98D001111738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="12">
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Inspector</t>
+  </si>
+  <si>
+    <t>Sede</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>Ítems</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>VILLA LOAIZA JHEISON ESTIBEN</t>
+  </si>
+  <si>
+    <t>CALDAS</t>
+  </si>
+  <si>
+    <t>JUAN DIEGO SANCHEZ</t>
+  </si>
+  <si>
+    <t>Guantes 🧤</t>
+  </si>
+  <si>
+    <t>PRUEBA</t>
+  </si>
+  <si>
+    <t>Guantes 🧤, Papelería general 📦</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +97,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,96 +401,491 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Inspector</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Sede</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Ítems</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>VILLA LOAIZA JHEISON ESTIBEN</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CALDAS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>JUAN DIEGO SANCHEZ</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Guantes 🧤</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>VILLA LOAIZA JHEISON ESTIBEN</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CALDAS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>PRUEBA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Guantes 🧤, Papelería general 📦</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>46088</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>46089</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>46103</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>Ítems</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Observación</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +474,7 @@
           <t>Guantes 🧤</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +502,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +530,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,6 +558,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -577,6 +586,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -604,6 +614,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -631,6 +642,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -658,6 +670,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -685,6 +698,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -712,6 +726,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -739,6 +754,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -766,6 +782,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -793,6 +810,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -820,6 +838,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -847,6 +866,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -874,6 +894,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -901,6 +922,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -928,6 +950,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -955,6 +978,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -982,6 +1006,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1009,6 +1034,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1036,6 +1062,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1063,6 +1090,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1090,6 +1118,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1117,6 +1146,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1144,6 +1174,7 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1171,6 +1202,35 @@
           <t>Guantes 🧤, Papelería general 📦</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ARIZA MARIN SERGIO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x30, Guantes 🧤 x1, Piernera 🦿 x1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1186,6 +1186,34 @@
       </c>
       <c r="F29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ARIZA MARIN SERGIO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>JUAN DIEGO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1214,6 +1214,34 @@
       </c>
       <c r="F30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ARIZA MARIN SERGIO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>JUAN DIEGO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Piernera 🦿 x12</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1242,6 +1242,34 @@
       </c>
       <c r="F31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ARIZA MARIN SERGIO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>JUAN DIEGO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x10</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -1,64 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962E926E-3B92-4BEE-B62A-DB9EB00D8050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Inspector</t>
-  </si>
-  <si>
-    <t>Sede</t>
-  </si>
-  <si>
-    <t>Responsable</t>
-  </si>
-  <si>
-    <t>Ítems</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -77,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -379,32 +408,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Inspector</t>
+        </is>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Sede</t>
+        </is>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Ítems</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,39 @@
           <t>Ítems</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Observación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RAMIREZ WILSON ENRIQUE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,34 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BEDOYA SANCHEZ CRISTIAN DAVID</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,34 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BORJAS WILLY ALEXANDER</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ANDRES ARROYAVE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,6 +531,34 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BUITRAGO RAMIREZ LEONARD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,6 +559,34 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>COBO HOYOS JUAN MANUEL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,6 +587,34 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RUIZ ARENAS JUAN CAMILO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ANDRES ARROYAVE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x80</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,6 +616,38 @@
       </c>
       <c r="F7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OSPINA CASTELLANOS ANDERSON</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>JUAN DIEGO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>30 Stiker para 60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,6 +648,34 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RUIZ DILON MARLON ANDREY</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ANDRES ARROYAVE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,6 +676,34 @@
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>OSPINA RODRIGUEZ DANIEL ALBERTO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,34 @@
       </c>
       <c r="F10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LOPEZ PINEDA CESAR AUGUSTO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RISARALDA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>JANIER</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x80</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,6 +732,34 @@
       </c>
       <c r="F11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>COGOLLO FIGUEROA RANDY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RISARALDA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DANNY DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x100</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,6 +760,34 @@
       </c>
       <c r="F12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GALLEGO CADAVID NORBEY</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RISARALDA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DANNY DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x100</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,34 @@
       </c>
       <c r="F13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ARIAS TORO YEISON</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RISARALDA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>JANIER</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x80</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -816,6 +816,34 @@
       </c>
       <c r="F14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AMAYA HINCAPIE JUAN CARLOS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x80</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,6 +844,34 @@
       </c>
       <c r="F15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AVENDAÑO GARCIA JUAN NEPOMUCENO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,6 +872,34 @@
       </c>
       <c r="F16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CARDONA CANO NELSON</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +900,34 @@
       </c>
       <c r="F17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CASTRO CASTAÑO JUAN DAVID</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,6 +928,34 @@
       </c>
       <c r="F18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GIRALDO GARCIA SIGIFREDO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -956,6 +956,34 @@
       </c>
       <c r="F19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OSPINA NARANJO BERNARDO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -984,6 +984,34 @@
       </c>
       <c r="F20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CASTRO CASTAÑO JUAN DAVID</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,6 +1012,34 @@
       </c>
       <c r="F21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>COBO HOYOS JUAN MANUEL</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,6 +1040,34 @@
       </c>
       <c r="F22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VILLA LOAIZA JHEISON ESTIBEN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1068,6 +1068,34 @@
       </c>
       <c r="F23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TAYACK TRUJILLO DEIVER EVELIO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x100</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1096,6 +1096,34 @@
       </c>
       <c r="F24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ANDRES ARROYAVE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ANDRES ARROYAVE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x80</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,34 @@
       </c>
       <c r="F25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OSPINA RODRIGUEZ DANIEL ALBERTO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1152,6 +1152,34 @@
       </c>
       <c r="F26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CARDONA CASTANO DIDIER ORLANDO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1180,6 +1180,34 @@
       </c>
       <c r="F27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RUIZ DILON MARLON ANDREY</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1208,6 +1208,34 @@
       </c>
       <c r="F28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BEDOYA SANCHEZ CRISTIAN DAVID</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ANDRES ARROYAVE</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1236,6 +1236,34 @@
       </c>
       <c r="F29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BORJAS WILLY ALEXANDER</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ANDRES ARROYAVE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x80</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1264,6 +1264,34 @@
       </c>
       <c r="F30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CARDONA CASTANO DIDIER ORLANDO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x80</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1292,6 +1292,34 @@
       </c>
       <c r="F31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CANO MORALES JIMY ALFREDO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Guantes 🧤 x1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1320,6 +1320,34 @@
       </c>
       <c r="F32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CHICA RAMIREZ CRISTIAN ALBERTO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Llaves de cepo 🗝️ x1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1348,6 +1348,34 @@
       </c>
       <c r="F33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ARIZA MARIN SERGIO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1376,6 +1376,34 @@
       </c>
       <c r="F34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BORJAS WILLY ALEXANDER</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>JUAN DIEGO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x80</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1404,6 +1404,34 @@
       </c>
       <c r="F35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AVENDAÑO GARCIA JUAN NEPOMUCENO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>JUAN DIEGO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1432,6 +1432,34 @@
       </c>
       <c r="F36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BUITRAGO RAMIREZ LEONARD</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1460,6 +1460,34 @@
       </c>
       <c r="F37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CARDONA CANO NELSON</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1488,6 +1488,34 @@
       </c>
       <c r="F38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CARDONA CASTANO DIDIER ORLANDO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1516,6 +1516,34 @@
       </c>
       <c r="F39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CASTRO CASTAÑO JUAN DAVID</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ANDRES ARROYAVE</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1544,6 +1544,34 @@
       </c>
       <c r="F40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>COBO HOYOS JUAN MANUEL</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1572,6 +1572,34 @@
       </c>
       <c r="F41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TAYACK TRUJILLO DEIVER EVELIO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ANDRES ARROYAVE</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x100</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1600,6 +1600,34 @@
       </c>
       <c r="F42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BEDOYA SANCHEZ CRISTIAN DAVID</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ANDRES ARROYAVE</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x50</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1628,6 +1628,34 @@
       </c>
       <c r="F43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CANO MORALES JIMY ALFREDO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ANDRES ARROYAVE</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Stickers 🔵 x60</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1656,6 +1656,34 @@
       </c>
       <c r="F44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CARDONA CANO NELSON</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ANDRES ARROYAVE</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Cepo 🔒 x3</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1684,6 +1684,34 @@
       </c>
       <c r="F45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CASTRO CASTAÑO JUAN DAVID</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CRISTIAN CHICA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Cepo 🔒 x3</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1712,6 +1712,34 @@
       </c>
       <c r="F46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ARIZA MARIN SERGIO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ANDRES ARROYAVE</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Cepo 🔒 x3</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
